--- a/novo projeto/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-29).xlsx
+++ b/novo projeto/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-29).xlsx
@@ -935,43 +935,43 @@
     <t>214</t>
   </si>
   <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>R$ 4.938,57</t>
-  </si>
-  <si>
-    <t>52.0</t>
-  </si>
-  <si>
-    <t>30.2</t>
-  </si>
-  <si>
-    <t>5.41</t>
-  </si>
-  <si>
-    <t>18.6</t>
+    <t>28</t>
+  </si>
+  <si>
+    <t>R$ 4.893,99</t>
+  </si>
+  <si>
+    <t>51.5</t>
+  </si>
+  <si>
+    <t>30.1</t>
+  </si>
+  <si>
+    <t>5.43</t>
+  </si>
+  <si>
+    <t>18.7</t>
   </si>
   <si>
     <t>6.6</t>
   </si>
   <si>
-    <t>6.0</t>
-  </si>
-  <si>
-    <t>41.3%</t>
-  </si>
-  <si>
-    <t>16.5%</t>
-  </si>
-  <si>
-    <t>1.8%</t>
+    <t>6.2</t>
+  </si>
+  <si>
+    <t>40.8%</t>
+  </si>
+  <si>
+    <t>16.3%</t>
+  </si>
+  <si>
+    <t>1.9%</t>
   </si>
   <si>
     <t>0.5%</t>
   </si>
   <si>
-    <t>3.9%</t>
+    <t>3.8%</t>
   </si>
   <si>
     <t>1.2%</t>
@@ -980,40 +980,40 @@
     <t>0.3%</t>
   </si>
   <si>
-    <t>6.5%</t>
+    <t>6.4%</t>
   </si>
   <si>
     <t>2.7%</t>
   </si>
   <si>
-    <t>3.5%</t>
-  </si>
-  <si>
-    <t>1110.0</t>
-  </si>
-  <si>
-    <t>894.0</t>
-  </si>
-  <si>
-    <t>99.0</t>
+    <t>3.4%</t>
+  </si>
+  <si>
+    <t>1127.0</t>
+  </si>
+  <si>
+    <t>905.0</t>
+  </si>
+  <si>
+    <t>103.0</t>
   </si>
   <si>
     <t>28.0</t>
   </si>
   <si>
-    <t>211.0</t>
-  </si>
-  <si>
-    <t>67.0</t>
-  </si>
-  <si>
-    <t>14.0</t>
-  </si>
-  <si>
-    <t>350.0</t>
-  </si>
-  <si>
-    <t>145.0</t>
+    <t>213.0</t>
+  </si>
+  <si>
+    <t>69.0</t>
+  </si>
+  <si>
+    <t>15.0</t>
+  </si>
+  <si>
+    <t>353.0</t>
+  </si>
+  <si>
+    <t>148.0</t>
   </si>
   <si>
     <t>188.0</t>
@@ -1022,7 +1022,7 @@
     <t>0.7%</t>
   </si>
   <si>
-    <t>36.0</t>
+    <t>38.0</t>
   </si>
   <si>
     <t>1</t>
@@ -6785,7 +6785,7 @@
         <v>19562</v>
       </c>
       <c r="B36" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C36" s="4">
         <v>51</v>
@@ -6815,35 +6815,93 @@
         <v>58</v>
       </c>
       <c r="L36" s="4"/>
-      <c r="M36" s="5"/>
-      <c r="N36" s="6"/>
-      <c r="O36" s="6"/>
-      <c r="P36" s="7"/>
-      <c r="Q36" s="8"/>
-      <c r="R36" s="8"/>
-      <c r="S36" s="8"/>
-      <c r="T36" s="9"/>
-      <c r="U36" s="9"/>
-      <c r="V36" s="9"/>
-      <c r="W36" s="9"/>
-      <c r="X36" s="9"/>
-      <c r="Y36" s="9"/>
-      <c r="Z36" s="9"/>
-      <c r="AA36" s="9"/>
-      <c r="AB36" s="9"/>
-      <c r="AC36" s="9"/>
-      <c r="AD36" s="6"/>
-      <c r="AE36" s="6"/>
-      <c r="AF36" s="6"/>
-      <c r="AG36" s="6"/>
-      <c r="AH36" s="6"/>
-      <c r="AI36" s="6"/>
-      <c r="AJ36" s="6"/>
-      <c r="AK36" s="6"/>
-      <c r="AL36" s="6"/>
-      <c r="AM36" s="6"/>
-      <c r="AN36" s="9"/>
-      <c r="AO36" s="6"/>
+      <c r="M36" s="5">
+        <v>4367.1099999999997</v>
+      </c>
+      <c r="N36" s="6">
+        <v>43</v>
+      </c>
+      <c r="O36" s="6">
+        <v>25</v>
+      </c>
+      <c r="P36" s="7">
+        <v>6.7746204545454551</v>
+      </c>
+      <c r="Q36" s="8">
+        <v>25.765331999999997</v>
+      </c>
+      <c r="R36" s="8">
+        <v>12.218054166666667</v>
+      </c>
+      <c r="S36" s="8">
+        <v>7</v>
+      </c>
+      <c r="T36" s="9">
+        <v>0.44</v>
+      </c>
+      <c r="U36" s="9">
+        <v>0.12</v>
+      </c>
+      <c r="V36" s="9">
+        <v>0.080000000000000002</v>
+      </c>
+      <c r="W36" s="9">
+        <v>0</v>
+      </c>
+      <c r="X36" s="9">
+        <v>0.040000000000000001</v>
+      </c>
+      <c r="Y36" s="9">
+        <v>0.040000000000000001</v>
+      </c>
+      <c r="Z36" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA36" s="9">
+        <v>0.040000000000000001</v>
+      </c>
+      <c r="AB36" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC36" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD36" s="6">
+        <v>5</v>
+      </c>
+      <c r="AE36" s="6">
+        <v>3</v>
+      </c>
+      <c r="AF36" s="6">
+        <v>2</v>
+      </c>
+      <c r="AG36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH36" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI36" s="6">
+        <v>1</v>
+      </c>
+      <c r="AJ36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK36" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN36" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO36" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP36" s="4">
         <v>58</v>
       </c>
@@ -7667,7 +7725,7 @@
         <v>19579</v>
       </c>
       <c r="B42" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C42" s="4">
         <v>51</v>
@@ -7697,35 +7755,93 @@
         <v>58</v>
       </c>
       <c r="L42" s="4"/>
-      <c r="M42" s="5"/>
-      <c r="N42" s="6"/>
-      <c r="O42" s="6"/>
-      <c r="P42" s="7"/>
-      <c r="Q42" s="8"/>
-      <c r="R42" s="8"/>
-      <c r="S42" s="8"/>
-      <c r="T42" s="9"/>
-      <c r="U42" s="9"/>
-      <c r="V42" s="9"/>
-      <c r="W42" s="9"/>
-      <c r="X42" s="9"/>
-      <c r="Y42" s="9"/>
-      <c r="Z42" s="9"/>
-      <c r="AA42" s="9"/>
-      <c r="AB42" s="9"/>
-      <c r="AC42" s="9"/>
-      <c r="AD42" s="6"/>
-      <c r="AE42" s="6"/>
-      <c r="AF42" s="6"/>
-      <c r="AG42" s="6"/>
-      <c r="AH42" s="6"/>
-      <c r="AI42" s="6"/>
-      <c r="AJ42" s="6"/>
-      <c r="AK42" s="6"/>
-      <c r="AL42" s="6"/>
-      <c r="AM42" s="6"/>
-      <c r="AN42" s="9"/>
-      <c r="AO42" s="6"/>
+      <c r="M42" s="5">
+        <v>4331.0799999999999</v>
+      </c>
+      <c r="N42" s="6">
+        <v>51</v>
+      </c>
+      <c r="O42" s="6">
+        <v>32</v>
+      </c>
+      <c r="P42" s="7">
+        <v>6.2634744680851071</v>
+      </c>
+      <c r="Q42" s="8">
+        <v>21.276562500000001</v>
+      </c>
+      <c r="R42" s="8">
+        <v>7.1338531249999999</v>
+      </c>
+      <c r="S42" s="8">
+        <v>7</v>
+      </c>
+      <c r="T42" s="9">
+        <v>0.25</v>
+      </c>
+      <c r="U42" s="9">
+        <v>0.0625</v>
+      </c>
+      <c r="V42" s="9">
+        <v>0</v>
+      </c>
+      <c r="W42" s="9">
+        <v>0</v>
+      </c>
+      <c r="X42" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y42" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA42" s="9">
+        <v>0.03125</v>
+      </c>
+      <c r="AB42" s="9">
+        <v>0.03125</v>
+      </c>
+      <c r="AC42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD42" s="6">
+        <v>2</v>
+      </c>
+      <c r="AE42" s="6">
+        <v>2</v>
+      </c>
+      <c r="AF42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK42" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL42" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO42" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP42" s="4">
         <v>58</v>
       </c>
@@ -9016,7 +9132,7 @@
         <v>19602</v>
       </c>
       <c r="B51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C51" s="4">
         <v>51</v>
@@ -9046,35 +9162,93 @@
         <v>58</v>
       </c>
       <c r="L51" s="4"/>
-      <c r="M51" s="5"/>
-      <c r="N51" s="6"/>
-      <c r="O51" s="6"/>
-      <c r="P51" s="7"/>
-      <c r="Q51" s="8"/>
-      <c r="R51" s="8"/>
-      <c r="S51" s="8"/>
-      <c r="T51" s="9"/>
-      <c r="U51" s="9"/>
-      <c r="V51" s="9"/>
-      <c r="W51" s="9"/>
-      <c r="X51" s="9"/>
-      <c r="Y51" s="9"/>
-      <c r="Z51" s="9"/>
-      <c r="AA51" s="9"/>
-      <c r="AB51" s="9"/>
-      <c r="AC51" s="9"/>
-      <c r="AD51" s="6"/>
-      <c r="AE51" s="6"/>
-      <c r="AF51" s="6"/>
-      <c r="AG51" s="6"/>
-      <c r="AH51" s="6"/>
-      <c r="AI51" s="6"/>
-      <c r="AJ51" s="6"/>
-      <c r="AK51" s="6"/>
-      <c r="AL51" s="6"/>
-      <c r="AM51" s="6"/>
-      <c r="AN51" s="9"/>
-      <c r="AO51" s="6"/>
+      <c r="M51" s="5">
+        <v>980.60000000000002</v>
+      </c>
+      <c r="N51" s="6">
+        <v>9</v>
+      </c>
+      <c r="O51" s="6">
+        <v>5</v>
+      </c>
+      <c r="P51" s="7">
+        <v>3.9799999999999995</v>
+      </c>
+      <c r="Q51" s="8">
+        <v>18.953340000000001</v>
+      </c>
+      <c r="R51" s="8">
+        <v>8.8133400000000002</v>
+      </c>
+      <c r="S51" s="8">
+        <v>7</v>
+      </c>
+      <c r="T51" s="9">
+        <v>0.40000000000000002</v>
+      </c>
+      <c r="U51" s="9">
+        <v>0.20000000000000001</v>
+      </c>
+      <c r="V51" s="9">
+        <v>0</v>
+      </c>
+      <c r="W51" s="9">
+        <v>0</v>
+      </c>
+      <c r="X51" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y51" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z51" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA51" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB51" s="9">
+        <v>0.20000000000000001</v>
+      </c>
+      <c r="AC51" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD51" s="6">
+        <v>1</v>
+      </c>
+      <c r="AE51" s="6">
+        <v>1</v>
+      </c>
+      <c r="AF51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL51" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN51" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO51" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP51" s="4">
         <v>58</v>
       </c>
@@ -10085,33 +10259,79 @@
       <c r="L58" s="4"/>
       <c r="M58" s="5"/>
       <c r="N58" s="6"/>
-      <c r="O58" s="6"/>
+      <c r="O58" s="6">
+        <v>50</v>
+      </c>
       <c r="P58" s="7"/>
       <c r="Q58" s="8"/>
       <c r="R58" s="8"/>
-      <c r="S58" s="8"/>
+      <c r="S58" s="8">
+        <v>7</v>
+      </c>
       <c r="T58" s="9"/>
-      <c r="U58" s="9"/>
-      <c r="V58" s="9"/>
-      <c r="W58" s="9"/>
-      <c r="X58" s="9"/>
-      <c r="Y58" s="9"/>
-      <c r="Z58" s="9"/>
-      <c r="AA58" s="9"/>
-      <c r="AB58" s="9"/>
-      <c r="AC58" s="9"/>
-      <c r="AD58" s="6"/>
-      <c r="AE58" s="6"/>
-      <c r="AF58" s="6"/>
-      <c r="AG58" s="6"/>
-      <c r="AH58" s="6"/>
-      <c r="AI58" s="6"/>
-      <c r="AJ58" s="6"/>
-      <c r="AK58" s="6"/>
-      <c r="AL58" s="6"/>
-      <c r="AM58" s="6"/>
-      <c r="AN58" s="9"/>
-      <c r="AO58" s="6"/>
+      <c r="U58" s="9">
+        <v>0.059999999999999998</v>
+      </c>
+      <c r="V58" s="9">
+        <v>0</v>
+      </c>
+      <c r="W58" s="9">
+        <v>0</v>
+      </c>
+      <c r="X58" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y58" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z58" s="9">
+        <v>0.02</v>
+      </c>
+      <c r="AA58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD58" s="6">
+        <v>3</v>
+      </c>
+      <c r="AE58" s="6">
+        <v>3</v>
+      </c>
+      <c r="AF58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ58" s="6">
+        <v>1</v>
+      </c>
+      <c r="AK58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN58" s="9">
+        <v>0.040000000000000001</v>
+      </c>
+      <c r="AO58" s="6">
+        <v>2</v>
+      </c>
       <c t="s" r="AP58" s="4">
         <v>58</v>
       </c>
@@ -16573,7 +16793,7 @@
         <v>19719</v>
       </c>
       <c r="B102" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C102" s="4">
         <v>51</v>
@@ -16603,35 +16823,93 @@
         <v>58</v>
       </c>
       <c r="L102" s="4"/>
-      <c r="M102" s="5"/>
-      <c r="N102" s="6"/>
-      <c r="O102" s="6"/>
-      <c r="P102" s="7"/>
-      <c r="Q102" s="8"/>
-      <c r="R102" s="8"/>
-      <c r="S102" s="8"/>
-      <c r="T102" s="9"/>
-      <c r="U102" s="9"/>
-      <c r="V102" s="9"/>
-      <c r="W102" s="9"/>
-      <c r="X102" s="9"/>
-      <c r="Y102" s="9"/>
-      <c r="Z102" s="9"/>
-      <c r="AA102" s="9"/>
-      <c r="AB102" s="9"/>
-      <c r="AC102" s="9"/>
-      <c r="AD102" s="6"/>
-      <c r="AE102" s="6"/>
-      <c r="AF102" s="6"/>
-      <c r="AG102" s="6"/>
-      <c r="AH102" s="6"/>
-      <c r="AI102" s="6"/>
-      <c r="AJ102" s="6"/>
-      <c r="AK102" s="6"/>
-      <c r="AL102" s="6"/>
-      <c r="AM102" s="6"/>
-      <c r="AN102" s="9"/>
-      <c r="AO102" s="6"/>
+      <c r="M102" s="5">
+        <v>2280.3099999999999</v>
+      </c>
+      <c r="N102" s="6">
+        <v>23</v>
+      </c>
+      <c r="O102" s="6">
+        <v>18</v>
+      </c>
+      <c r="P102" s="7">
+        <v>6.6388875000000001</v>
+      </c>
+      <c r="Q102" s="8">
+        <v>21.79815</v>
+      </c>
+      <c r="R102" s="8">
+        <v>8.9813705882352934</v>
+      </c>
+      <c r="S102" s="8">
+        <v>7</v>
+      </c>
+      <c r="T102" s="9">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="U102" s="9">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="V102" s="9">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="W102" s="9">
+        <v>0</v>
+      </c>
+      <c r="X102" s="9">
+        <v>0.055555555555555552</v>
+      </c>
+      <c r="Y102" s="9">
+        <v>0.055555555555555552</v>
+      </c>
+      <c r="Z102" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA102" s="9">
+        <v>0.055555555555555552</v>
+      </c>
+      <c r="AB102" s="9">
+        <v>0.055555555555555552</v>
+      </c>
+      <c r="AC102" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD102" s="6">
+        <v>6</v>
+      </c>
+      <c r="AE102" s="6">
+        <v>2</v>
+      </c>
+      <c r="AF102" s="6">
+        <v>2</v>
+      </c>
+      <c r="AG102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH102" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI102" s="6">
+        <v>1</v>
+      </c>
+      <c r="AJ102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK102" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL102" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN102" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO102" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP102" s="4">
         <v>58</v>
       </c>
@@ -30382,7 +30660,7 @@
         <v>19944</v>
       </c>
       <c r="B195" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C195" s="4">
         <v>51</v>
@@ -30412,14 +30690,26 @@
         <v>58</v>
       </c>
       <c r="L195" s="4"/>
-      <c r="M195" s="5"/>
-      <c r="N195" s="6"/>
+      <c r="M195" s="5">
+        <v>4442.3599999999997</v>
+      </c>
+      <c r="N195" s="6">
+        <v>51</v>
+      </c>
       <c r="O195" s="6"/>
-      <c r="P195" s="7"/>
-      <c r="Q195" s="8"/>
-      <c r="R195" s="8"/>
+      <c r="P195" s="7">
+        <v>6.3996369565217393</v>
+      </c>
+      <c r="Q195" s="8">
+        <v>22.025521874999999</v>
+      </c>
+      <c r="R195" s="8">
+        <v>8.0656250000000007</v>
+      </c>
       <c r="S195" s="8"/>
-      <c r="T195" s="9"/>
+      <c r="T195" s="9">
+        <v>0.15625</v>
+      </c>
       <c r="U195" s="9"/>
       <c r="V195" s="9"/>
       <c r="W195" s="9"/>
